--- a/VerveStacks_DNK_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_DNK_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DNK_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D2684B57-4084-425B-912F-6F084861FA29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0003E13F-6C33-435A-BAFA-147F5B80B0AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -125,7 +125,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3394" uniqueCount="500">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3384" uniqueCount="497">
   <si>
     <t>~TFM_INS-AT</t>
   </si>
@@ -1623,15 +1623,6 @@
   </si>
   <si>
     <t>STG</t>
-  </si>
-  <si>
-    <t>Trd_electricity import</t>
-  </si>
-  <si>
-    <t>e_DK1-400,e_DK16-400,e_DK19-400,e_DK2-400,e_DK21-400,e_DK22-220,e_DK26-400,e_DK27-400,e_DK3-400,e_DK4-400,e_DK5-400,e_DK6-220,e_w131339683-400,e_w133555503-400,e_w1384028957,e_w1384028957-400,e_w199713891-400,e_w250212215-400,e_w26931725-220,e_w26931725-400,e_w301369285-400,e_w42128776-400,e_w93624851-400,e_w94092312-400,e_w98212652-400,e_w98216482,e_w98216482-400</t>
-  </si>
-  <si>
-    <t>Trd_electricity export</t>
   </si>
 </sst>
 </file>
@@ -2846,10 +2837,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76C252B5-B709-4006-BF20-3EB56F1CA4B4}">
-  <dimension ref="B2:AJ209"/>
+  <dimension ref="B2:AF209"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="2" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -2862,11 +2853,8 @@
       <c r="U2" t="s">
         <v>247</v>
       </c>
-      <c r="AH2" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="3" spans="2:36" x14ac:dyDescent="0.45">
+    </row>
+    <row r="3" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B3" t="s">
         <v>3</v>
       </c>
@@ -2918,17 +2906,8 @@
       <c r="AA3" t="s">
         <v>193</v>
       </c>
-      <c r="AH3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AI3" t="s">
-        <v>194</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="4" spans="2:36" x14ac:dyDescent="0.45">
+    </row>
+    <row r="4" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B4" t="s">
         <v>133</v>
       </c>
@@ -2995,17 +2974,8 @@
       <c r="AF4" t="s">
         <v>494</v>
       </c>
-      <c r="AH4" t="s">
-        <v>497</v>
-      </c>
-      <c r="AI4" t="s">
-        <v>498</v>
-      </c>
-      <c r="AJ4" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="5" spans="2:36" x14ac:dyDescent="0.45">
+    </row>
+    <row r="5" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
         <v>134</v>
       </c>
@@ -3069,17 +3039,8 @@
       <c r="AF5" t="s">
         <v>495</v>
       </c>
-      <c r="AH5" t="s">
-        <v>499</v>
-      </c>
-      <c r="AI5" t="s">
-        <v>498</v>
-      </c>
-      <c r="AJ5" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="6" spans="2:36" x14ac:dyDescent="0.45">
+    </row>
+    <row r="6" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B6" t="s">
         <v>135</v>
       </c>
@@ -3144,7 +3105,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="7" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B7" t="s">
         <v>136</v>
       </c>
@@ -3194,7 +3155,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="8" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B8" t="s">
         <v>137</v>
       </c>
@@ -3244,7 +3205,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="9" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
         <v>138</v>
       </c>
@@ -3294,7 +3255,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="10" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
         <v>139</v>
       </c>
@@ -3344,7 +3305,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="11" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
         <v>140</v>
       </c>
@@ -3394,7 +3355,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="12" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
         <v>141</v>
       </c>
@@ -3444,7 +3405,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="13" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
         <v>142</v>
       </c>
@@ -3494,7 +3455,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="14" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
         <v>143</v>
       </c>
@@ -3544,7 +3505,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="15" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
         <v>144</v>
       </c>
@@ -3594,7 +3555,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="16" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
         <v>145</v>
       </c>
